--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -1545,6 +1545,9 @@
           <t>årsunge</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bånghammar, Bånghammar, Vstm</t>
@@ -1605,6 +1608,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641390</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641438</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641519</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657594</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1624,6 +1664,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641666</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1745,6 +1790,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641705</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641876</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1987,8 +2042,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642276</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134641330</v>
+        <v>135661540</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,24 +713,39 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bånghammar, Bånghammar, Vstm</t>
+          <t>Lundtorp, Lundtorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500604</v>
+        <v>500450</v>
       </c>
       <c r="R2" t="n">
-        <v>6635957</v>
+        <v>6636042</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +769,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack med savflöde</t>
+          <t>Trumning och rop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,13 +815,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641330</t>
+          <t>https://artportalen.se/Sighting/135661540</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134641390</v>
+        <v>134641330</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -834,7 +849,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -846,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500607</v>
+        <v>500604</v>
       </c>
       <c r="R3" t="n">
-        <v>6635943</v>
+        <v>6635957</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +910,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färsk barkfläkning och ringhack med savflöde</t>
+          <t>Färska ringhack med savflöde</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,13 +941,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641390</t>
+          <t>https://artportalen.se/Sighting/134641330</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134641413</v>
+        <v>134641390</v>
       </c>
       <c r="B4" t="n">
         <v>57975</v>
@@ -968,10 +987,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500600</v>
+        <v>500607</v>
       </c>
       <c r="R4" t="n">
-        <v>6635950</v>
+        <v>6635943</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1044,13 +1063,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641413</t>
+          <t>https://artportalen.se/Sighting/134641390</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134641438</v>
+        <v>134641413</v>
       </c>
       <c r="B5" t="n">
         <v>57975</v>
@@ -1090,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500603</v>
+        <v>500600</v>
       </c>
       <c r="R5" t="n">
-        <v>6635952</v>
+        <v>6635950</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1125,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,12 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färsk barkfläkning på ytterligare 2 granar</t>
+          <t>Färsk barkfläkning och ringhack med savflöde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,13 +1185,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641438</t>
+          <t>https://artportalen.se/Sighting/134641413</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134641501</v>
+        <v>134641438</v>
       </c>
       <c r="B6" t="n">
         <v>57975</v>
@@ -1212,10 +1231,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500602</v>
+        <v>500603</v>
       </c>
       <c r="R6" t="n">
-        <v>6635985</v>
+        <v>6635952</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1247,7 +1266,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,12 +1276,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färsk barkfläkning och ringhack med savflöde</t>
+          <t>Färsk barkfläkning på ytterligare 2 granar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,13 +1307,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641501</t>
+          <t>https://artportalen.se/Sighting/134641438</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134641519</v>
+        <v>134641501</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1334,10 +1353,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500601</v>
+        <v>500602</v>
       </c>
       <c r="R7" t="n">
-        <v>6635979</v>
+        <v>6635985</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1369,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1398,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färsk barkfläkning och ringhack med savflöde.</t>
+          <t>Färsk barkfläkning och ringhack med savflöde</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,70 +1429,56 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641519</t>
+          <t>https://artportalen.se/Sighting/134641501</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134657594</v>
+        <v>134641519</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtbo, Jämtbo, Vstm</t>
+          <t>Bånghammar, Bånghammar, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500388</v>
+        <v>500601</v>
       </c>
       <c r="R8" t="n">
-        <v>6635717</v>
+        <v>6635979</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1503,14 +1508,24 @@
           <t>2026-06-25</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fjäder fr tjädertupp på vägen.</t>
+          <t>Färsk barkfläkning och ringhack med savflöde.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,16 +1551,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134657594</t>
+          <t>https://artportalen.se/Sighting/134641519</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134641666</v>
+        <v>134657594</v>
       </c>
       <c r="B9" t="n">
-        <v>58839</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,16 +1568,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1575,29 +1590,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bånghammar, Bånghammar, Vstm</t>
+          <t>Jämtbo, Jämtbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500551</v>
+        <v>500388</v>
       </c>
       <c r="R9" t="n">
-        <v>6635961</v>
+        <v>6635717</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1627,19 +1644,14 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjäder fr tjädertupp på vägen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1660,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,38 +1677,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641666</t>
+          <t>https://artportalen.se/Sighting/134657594</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134641705</v>
+        <v>135660450</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>58524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1705,26 +1716,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bånghammar, Bånghammar, Vstm</t>
+          <t>Lundtorp, Lundtorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500539</v>
+        <v>500449</v>
       </c>
       <c r="R10" t="n">
-        <v>6635988</v>
+        <v>6636031</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1751,22 +1772,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,38 +1813,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641705</t>
+          <t>https://artportalen.se/Sighting/135660450</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134641876</v>
+        <v>135660468</v>
       </c>
       <c r="B11" t="n">
-        <v>99112</v>
+        <v>58524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1831,26 +1852,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bånghammar, Bånghammar, Vstm</t>
+          <t>Lundtorp, Lundtorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500549</v>
+        <v>500450</v>
       </c>
       <c r="R11" t="n">
-        <v>6636035</v>
+        <v>6636042</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1877,22 +1908,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1918,16 +1949,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134641876</t>
+          <t>https://artportalen.se/Sighting/135660468</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134642276</v>
+        <v>135661690</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>58136</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,48 +1966,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>103023</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backarna, Backarna, Vstm</t>
+          <t>Lundtorp, Lundtorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500336</v>
+        <v>500450</v>
       </c>
       <c r="R12" t="n">
-        <v>6636073</v>
+        <v>6636042</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2003,22 +2034,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,6 +2074,514 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135661690</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134641666</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bånghammar, Bånghammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500551</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6635961</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641666</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134641705</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bånghammar, Bånghammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500539</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6635988</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641705</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134641876</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bånghammar, Bånghammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>500549</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6636035</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641876</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134642276</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Backarna, Backarna, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>500336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6636073</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134642276</t>
         </is>
@@ -2061,6 +2600,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661540</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135660450</v>
       </c>
       <c r="B10" t="n">
-        <v>58524</v>
+        <v>58526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135660468</v>
       </c>
       <c r="B11" t="n">
-        <v>58524</v>
+        <v>58526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>135661690</v>
       </c>
       <c r="B12" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661540</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135660450</v>
       </c>
       <c r="B10" t="n">
-        <v>58526</v>
+        <v>58527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135660468</v>
       </c>
       <c r="B11" t="n">
-        <v>58526</v>
+        <v>58527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>135661690</v>
       </c>
       <c r="B12" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661540</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135660450</v>
       </c>
       <c r="B10" t="n">
-        <v>58527</v>
+        <v>58531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135660468</v>
       </c>
       <c r="B11" t="n">
-        <v>58527</v>
+        <v>58531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>135661690</v>
       </c>
       <c r="B12" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24307-2026 artfynd.xlsx
+++ b/artfynd/A 24307-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661540</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135660450</v>
       </c>
       <c r="B10" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135660468</v>
       </c>
       <c r="B11" t="n">
-        <v>58531</v>
+        <v>58532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>135661690</v>
       </c>
       <c r="B12" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
